--- a/artfynd/A 35507-2022 artfynd.xlsx
+++ b/artfynd/A 35507-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274360</v>
       </c>
       <c r="B2" t="n">
-        <v>92900</v>
+        <v>92906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136274371</v>
       </c>
       <c r="B3" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136274871</v>
       </c>
       <c r="B4" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35507-2022 artfynd.xlsx
+++ b/artfynd/A 35507-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274360</v>
       </c>
       <c r="B2" t="n">
-        <v>92906</v>
+        <v>92907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136274371</v>
       </c>
       <c r="B3" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136274871</v>
       </c>
       <c r="B4" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35507-2022 artfynd.xlsx
+++ b/artfynd/A 35507-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274360</v>
       </c>
       <c r="B2" t="n">
-        <v>92907</v>
+        <v>92913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136274371</v>
       </c>
       <c r="B3" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136274871</v>
       </c>
       <c r="B4" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35507-2022 artfynd.xlsx
+++ b/artfynd/A 35507-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274360</v>
       </c>
       <c r="B2" t="n">
-        <v>92913</v>
+        <v>92920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136274371</v>
       </c>
       <c r="B3" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136274871</v>
       </c>
       <c r="B4" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35507-2022 artfynd.xlsx
+++ b/artfynd/A 35507-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274360</v>
       </c>
       <c r="B2" t="n">
-        <v>92920</v>
+        <v>92921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136274871</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35507-2022 artfynd.xlsx
+++ b/artfynd/A 35507-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274360</v>
       </c>
       <c r="B2" t="n">
-        <v>92921</v>
+        <v>92934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136274371</v>
       </c>
       <c r="B3" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136274871</v>
       </c>
       <c r="B4" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35507-2022 artfynd.xlsx
+++ b/artfynd/A 35507-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274360</v>
       </c>
       <c r="B2" t="n">
-        <v>92934</v>
+        <v>92935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136274371</v>
       </c>
       <c r="B3" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136274871</v>
       </c>
       <c r="B4" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
